--- a/jainam/Ayush Keys - Copy.xlsx
+++ b/jainam/Ayush Keys - Copy.xlsx
@@ -1,26 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Rohan_Do_Not_Delete\Ayussh\godseye\jainam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chaitanya.padachh_in\Desktop\Driver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCA4A33-B6A6-4642-A19A-7FED66A330E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A95A48A-65A1-479D-A9B9-73660AC4362F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="3810" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="138">
+  <si>
+    <t>Unnamed: 0.1</t>
+  </si>
+  <si>
+    <t>Unnamed: 0</t>
+  </si>
   <si>
     <t>Name</t>
   </si>
@@ -61,56 +79,380 @@
     <t>ROC</t>
   </si>
   <si>
+    <t>Vinnie</t>
+  </si>
+  <si>
+    <t>6DIT30305</t>
+  </si>
+  <si>
+    <t>Ram@123</t>
+  </si>
+  <si>
+    <t>iVhWsbI7TB</t>
+  </si>
+  <si>
+    <t>Algo1</t>
+  </si>
+  <si>
+    <t>uLdwWfXEzgZSRbEfDmEP8L9eFzbHIt5eA1C2NNIKcS2Ivm8BjW7sgmXH9NsDYI5C</t>
+  </si>
+  <si>
+    <t>http://127.0.0.1:5000/</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
+    <t>Pro</t>
+  </si>
+  <si>
+    <t>ram456</t>
+  </si>
+  <si>
+    <t>PMNYLAIAZ3SFWUPG</t>
+  </si>
+  <si>
+    <t>caad78f1eefaf7d053e166</t>
+  </si>
+  <si>
+    <t>ProAlgo</t>
+  </si>
+  <si>
+    <t>Tytj877#Pw</t>
+  </si>
+  <si>
+    <t>Clean</t>
+  </si>
+  <si>
+    <t>SN253</t>
+  </si>
+  <si>
+    <t>Ram@234</t>
+  </si>
+  <si>
+    <t>3UGLFFNTUR2K5L5G5ZD5CLVBCI5RZ36IMSXJUC3H</t>
+  </si>
+  <si>
+    <t>GuV2xdFDZP</t>
+  </si>
+  <si>
+    <t>AgxKs97WhgpMIrqYsRdh0iG0RIgcetfZUiLHkFd2xU44rn5NLcOQ4Qj0fVcZv5uJ</t>
+  </si>
+  <si>
+    <t>Greenvalley!</t>
+  </si>
+  <si>
+    <t>SN190</t>
+  </si>
+  <si>
+    <t>5AJ5BQ3PLJ7COSFZKJIMJQB3TR6B7F65R6FC5FCF</t>
+  </si>
+  <si>
+    <t>JH7Ce7iJJK</t>
+  </si>
+  <si>
+    <t>LvRQ154pJ15z3jBNnQYXRD8iBbjWSyc232RBRxOgrEMG0cppPyn2oWfIutqW7ERP</t>
+  </si>
+  <si>
+    <t>https://127.0.0.1/</t>
+  </si>
+  <si>
+    <t>ANAM!</t>
+  </si>
+  <si>
+    <t>6DIT36623</t>
+  </si>
+  <si>
+    <t>WRWZYVWZK3MJ5GYLDS5423HHRL4V5NQNAPAPQLFJ</t>
+  </si>
+  <si>
+    <t>tCl6NcW8RG</t>
+  </si>
+  <si>
+    <t>zDHFUAx9JwejWZ6ZmJG9txYTOotE8X8I5QjUkGkkBtOxYyuV80mHgLwdKzgVd02v</t>
+  </si>
+  <si>
+    <t>gandhi1</t>
+  </si>
+  <si>
+    <t>1994</t>
+  </si>
+  <si>
+    <t>jD4AjOhxjD</t>
+  </si>
+  <si>
+    <t>Algo</t>
+  </si>
+  <si>
+    <t>s2MXRbgVwfgPQ8q1EbeN003kCXXUpZMdhOuNicDGvGmjpq1FGFK5Rm5JGToTxXUn</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Sumit</t>
+  </si>
+  <si>
+    <t>6DIT02</t>
+  </si>
+  <si>
+    <t>a1SrPXFukK</t>
+  </si>
+  <si>
+    <t>MyREC8ji3xuy8XHn6v4VRCw0CHgqHcJQS8uBiqbuOPqKI3rgBHnP7YkhWXtoTi1b</t>
+  </si>
+  <si>
+    <t>Sandeep!</t>
+  </si>
+  <si>
+    <t>6DIT03</t>
+  </si>
+  <si>
+    <t>WER7XCVVFODNHZKPDW66DAWXCGNDSTURWR4IKPO4</t>
+  </si>
+  <si>
+    <t>jUR0oqthJy</t>
+  </si>
+  <si>
+    <t>pg4YaEKHaTJ1IRk6n0PQ0btGsjibSMpAiIwydDs2SEVguxZPk1q4BnnfO8IXshia</t>
+  </si>
+  <si>
+    <t>Manorma!</t>
+  </si>
+  <si>
+    <t>6DIT04</t>
+  </si>
+  <si>
+    <t>CBK74HSGTA36LNSHLB7EZABENXS735VBNV5NZTSA</t>
+  </si>
+  <si>
+    <t>3GpWtaLxBg</t>
+  </si>
+  <si>
+    <t>2bcRb9EdhzegvjA11sGJvEdnwDImfXucUSpYy6g1RaOomado6Jux34v1qDZQDVl6</t>
+  </si>
+  <si>
+    <t>Seema</t>
+  </si>
+  <si>
+    <t>6DIT230</t>
+  </si>
+  <si>
+    <t>ram567</t>
+  </si>
+  <si>
+    <t>tnaOZY4mUy</t>
+  </si>
+  <si>
+    <t>8SsoqtjZHG8OouSuCw6wd3LEFOU2niRUmmBXAe7sDle61V3uz41C8zgl9z6Xcp09</t>
+  </si>
+  <si>
+    <t>Kunal</t>
+  </si>
+  <si>
+    <t>KH30</t>
+  </si>
+  <si>
+    <t>ram345</t>
+  </si>
+  <si>
+    <t>4e6ca429f874156afe5363</t>
+  </si>
+  <si>
+    <t>KunalAlgo</t>
+  </si>
+  <si>
+    <t>Greg427#Hp</t>
+  </si>
+  <si>
+    <t>Avantika</t>
+  </si>
+  <si>
+    <t>SN257</t>
+  </si>
+  <si>
+    <t>RMORBZSWFOJXOGFS</t>
+  </si>
+  <si>
+    <t>0ic5E9kBnV</t>
+  </si>
+  <si>
+    <t>Godseye</t>
+  </si>
+  <si>
+    <t>yXWR68FjtGn1I9hCQa2NbxtBd7qJlQlawukbFrm0NtsbMqNFmOUXTiyrqBx4nuCW</t>
+  </si>
+  <si>
     <t>http://127.0.0.1:5000</t>
   </si>
   <si>
+    <t>Shuja</t>
+  </si>
+  <si>
+    <t>6DIT05</t>
+  </si>
+  <si>
+    <t>HQ6YZCLBUAPBC5I4</t>
+  </si>
+  <si>
+    <t>GRTWx3TwqD</t>
+  </si>
+  <si>
+    <t>oNfEGpyAH0tJLksLFSqeSceHG6c00DCpkSgIvTuYpkYGvrPLhYl1D9tEsEj2Bek9</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>SN1009</t>
+  </si>
+  <si>
+    <t>HTQWYHIPRIDSNF6E</t>
+  </si>
+  <si>
+    <t>x9hZ68MOqo</t>
+  </si>
+  <si>
+    <t>sULnbD75SA2LLUqubEZJVZGDpVs4zd3GemegmNLvGjFKppa3IGzUyIL2LbXWXPgs</t>
+  </si>
+  <si>
+    <t>Sachin</t>
+  </si>
+  <si>
+    <t>6DIT10002</t>
+  </si>
+  <si>
+    <t>SQFKME6GP5EEH3AF</t>
+  </si>
+  <si>
+    <t>koobQPNFSA</t>
+  </si>
+  <si>
     <t>Goddseye</t>
   </si>
   <si>
+    <t>0DaLqX6KMUwJ9trbn5hZoxkQroillndlkkfYWVRFOQug7InqbQhwscELT3jVoKsM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROWTH </t>
+  </si>
+  <si>
+    <t>6DIT999</t>
+  </si>
+  <si>
+    <t>Igitb89wV3</t>
+  </si>
+  <si>
+    <t>tF3D4kGFufUBqaTZ0xkxQ5sCMpYxXPKskzlXn5prv4JNx4GjEUIPdIO92VlmirC9</t>
+  </si>
+  <si>
+    <t>DB44BFZNH4MDIZR3</t>
+  </si>
+  <si>
+    <t>Ram@345</t>
+  </si>
+  <si>
+    <t>*****</t>
+  </si>
+  <si>
+    <t>GIMLXIZYGP4OJQNC</t>
+  </si>
+  <si>
+    <t>RACHITA</t>
+  </si>
+  <si>
+    <t>SN11111</t>
+  </si>
+  <si>
+    <t>SDZ35EEUQZIA45AQ</t>
+  </si>
+  <si>
+    <t>lJzgmU511p</t>
+  </si>
+  <si>
+    <t>Goddseye Algo</t>
+  </si>
+  <si>
+    <t>PygdDKGx000Z9xEl5pggs78e6rw6CLrBXS2sem3Tx2t8CzTLFXhOiyQCS2kDErGG</t>
+  </si>
+  <si>
+    <t>Ram@456</t>
+  </si>
+  <si>
+    <t>VIJAY</t>
+  </si>
+  <si>
+    <t>JalbRXNaQH</t>
+  </si>
+  <si>
+    <t>6DIT2006</t>
+  </si>
+  <si>
+    <t>3VQML3QBGZ55E3DJ</t>
+  </si>
+  <si>
+    <t>0i9ytEGEMjH5ua74JsZW6NOtRp4pwkjd5y8VlaOVtH0ZWnBoFORXBubV6Ig2Bv4g</t>
+  </si>
+  <si>
+    <t>5F2FSBPOJMQXGMCZ</t>
+  </si>
+  <si>
+    <t>ANAM_JAINAM</t>
+  </si>
+  <si>
+    <t>ITC2317</t>
+  </si>
+  <si>
+    <t>1218698a0386fcb01be136</t>
+  </si>
+  <si>
+    <t>Rnfw568@g#</t>
+  </si>
+  <si>
+    <t>SHUJA_JAINAM</t>
+  </si>
+  <si>
+    <t>ITC2319</t>
+  </si>
+  <si>
+    <t>2a36a98b302bd034518495</t>
+  </si>
+  <si>
+    <t>Hsik733#vS</t>
+  </si>
+  <si>
+    <t>CLEAN_JAINAM</t>
+  </si>
+  <si>
+    <t>5b22950ea39e7fc9dd8340</t>
+  </si>
+  <si>
+    <t>Foue023#nL</t>
+  </si>
+  <si>
+    <t>Am@234</t>
+  </si>
+  <si>
+    <t>ITC2275</t>
+  </si>
+  <si>
     <t>IFTIKHAR_JAINAM</t>
   </si>
   <si>
     <t>ITC2851</t>
   </si>
   <si>
-    <t>Am@234</t>
-  </si>
-  <si>
     <t>0ba5b6786d645e2c4ec814</t>
   </si>
   <si>
     <t>Lvve826@yi</t>
-  </si>
-  <si>
-    <t>RACHITA</t>
-  </si>
-  <si>
-    <t>SN11111</t>
-  </si>
-  <si>
-    <t>Ram@345</t>
-  </si>
-  <si>
-    <t>SDZ35EEUQZIA45AQ</t>
-  </si>
-  <si>
-    <t>lJzgmU511p</t>
-  </si>
-  <si>
-    <t>Goddseye Algo</t>
-  </si>
-  <si>
-    <t>PygdDKGx000Z9xEl5pggs78e6rw6CLrBXS2sem3Tx2t8CzTLFXhOiyQCS2kDErGG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,14 +494,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF3C3C3C"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -200,7 +535,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -210,7 +545,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -514,25 +848,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="71.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -572,120 +895,930 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="E3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s">
+        <v>51</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L10" t="s">
+        <v>51</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" t="s">
+        <v>51</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" t="s">
+        <v>51</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
+        <v>81</v>
+      </c>
+      <c r="I14" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14">
+        <v>8</v>
+      </c>
+      <c r="K14" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" t="s">
+        <v>51</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15">
+        <v>12</v>
+      </c>
+      <c r="K15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L15" t="s">
+        <v>51</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16" t="s">
+        <v>99</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L16" t="s">
+        <v>51</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17" t="s">
+        <v>83</v>
+      </c>
+      <c r="L17" t="s">
+        <v>22</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" t="s">
+        <v>83</v>
+      </c>
+      <c r="L18" t="s">
+        <v>22</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" t="s">
+        <v>83</v>
+      </c>
+      <c r="L19" t="s">
+        <v>22</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L20" t="s">
+        <v>22</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>18</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B21">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I21" t="s">
+        <v>128</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
+        <v>83</v>
+      </c>
+      <c r="L21" t="s">
+        <v>22</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>19</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="B22">
         <v>19</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="C22" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F22" t="s">
+        <v>130</v>
+      </c>
+      <c r="G22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I22" t="s">
+        <v>131</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22" t="s">
+        <v>83</v>
+      </c>
+      <c r="L22" t="s">
+        <v>22</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>20</v>
       </c>
-      <c r="H2" s="6">
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>134</v>
+      </c>
+      <c r="D23" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" t="s">
+        <v>136</v>
+      </c>
+      <c r="G23" t="s">
+        <v>136</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I23" t="s">
+        <v>137</v>
+      </c>
+      <c r="J23">
         <v>2</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="K23" t="s">
+        <v>83</v>
+      </c>
+      <c r="L23" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C5" s="2"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C9" s="2"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="5"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="12" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C13" s="2"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C14" s="2"/>
-      <c r="F14" s="3"/>
+      <c r="O23">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="mailto:Am@234" xr:uid="{33BC352A-7C81-4B4E-879D-7EAB13C3F5D8}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{A1A336C6-B8EB-46D9-AF39-6CA164C87317}"/>
+    <hyperlink ref="E16" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E14" r:id="rId2" xr:uid="{6EE71651-26BC-43A8-B65A-A61D5D15F135}"/>
+    <hyperlink ref="E2" r:id="rId3" xr:uid="{0096F8DF-EE4C-40A5-AB4F-D14F08A1B353}"/>
+    <hyperlink ref="E13" r:id="rId4" xr:uid="{D4A06928-0279-4067-AE80-0331E098EC5D}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{11DCFF1A-011C-453F-8407-E13F132E33AC}"/>
+    <hyperlink ref="E8" r:id="rId6" xr:uid="{1B31C4A5-3D4E-4AC5-B8D9-44E6DFC12F62}"/>
+    <hyperlink ref="E18" r:id="rId7" xr:uid="{56EC05EF-4F2B-48CB-B074-E88EA586BA83}"/>
+    <hyperlink ref="E5" r:id="rId8" xr:uid="{B0A864B5-D717-4384-AB46-8428C0B65D6A}"/>
+    <hyperlink ref="E3" r:id="rId9" xr:uid="{CA3FCE89-3C38-43A6-B971-F34208C0E5DA}"/>
+    <hyperlink ref="E22" r:id="rId10" xr:uid="{41C44775-0E92-42FD-B387-87EB027134DB}"/>
+    <hyperlink ref="E23" r:id="rId11" xr:uid="{BCB44680-E633-44FD-AC11-AB25BE5E9D80}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>